--- a/docs/downloads/经营分_津河省区__廊坊片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_津河省区__廊坊片区_2026-10-18.xlsx
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1287,22 +1287,22 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7279360098319730725</t>
+          <t>6934441132961056783</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>潮漫酒店·三河燕郊沃尔玛店</t>
+          <t>维也纳智好酒店（河北廊坊红楼梦戏剧幻城肿瘤医院国际会展中心店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>潮漫酒店三河燕郊沃尔玛店</t>
+          <t>维也纳智好酒店(国际会展中心店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1375,17 +1375,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6934441132961056783</t>
+          <t>7279360098319730725</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>维也纳智好酒店（河北廊坊红楼梦戏剧幻城肿瘤医院国际会展中心店）</t>
+          <t>潮漫酒店·三河燕郊沃尔玛店</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>维也纳智好酒店(国际会展中心店)</t>
+          <t>潮漫酒店三河燕郊沃尔玛店</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I10" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>30</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
         <v>30</v>
@@ -1463,17 +1463,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>7243284687827765281</t>
+          <t>6763198105849464840</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7天酒店（文安左各庄南二环大柳河高速口店）</t>
+          <t>麗枫酒店·三河燕郊天洋广场店</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7天酒店(文安左各庄南二环大柳河高速口店)</t>
+          <t>麗枫酒店(三河燕郊天洋广场店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I11" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1499,13 +1499,13 @@
         <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N11" t="n">
         <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P11" t="n">
         <v>30</v>
@@ -1551,17 +1551,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>6675265034328786956</t>
+          <t>7243284687827765281</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>河北廊坊霸州市益津南路店</t>
+          <t>7天酒店（文安左各庄南二环大柳河高速口店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>维也纳酒店(河北廊坊霸州益津南路店)</t>
+          <t>7天酒店(文安左各庄南二环大柳河高速口店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1573,7 +1573,7 @@
         <v>90</v>
       </c>
       <c r="I12" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1587,13 +1587,13 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
+        <v>20</v>
+      </c>
+      <c r="N12" t="n">
+        <v>30</v>
+      </c>
+      <c r="O12" t="n">
         <v>25</v>
-      </c>
-      <c r="N12" t="n">
-        <v>30</v>
-      </c>
-      <c r="O12" t="n">
-        <v>20</v>
       </c>
       <c r="P12" t="n">
         <v>30</v>
@@ -1639,29 +1639,29 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>6819939457265895424</t>
+          <t>6675265034328786956</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>派酒店（廊坊固安县政府南关夜市店）</t>
+          <t>河北廊坊霸州市益津南路店</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>派酒店(廊坊固安店)</t>
+          <t>维也纳酒店(河北廊坊霸州益津南路店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>90</v>
       </c>
       <c r="I13" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N13" t="n">
         <v>30</v>
@@ -1687,7 +1687,7 @@
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R13" t="n">
         <v>30</v>
@@ -1727,61 +1727,61 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7582050881475086371</t>
+          <t>6819939457265895424</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>丽枫酒店(廊坊中国医学科学院肿瘤医院店)</t>
+          <t>派酒店（廊坊固安县政府南关夜市店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>丽枫酒店(廊坊中国医学科学院肿瘤医院店)</t>
+          <t>派酒店(廊坊固安店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>-2</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N14" t="n">
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P14" t="n">
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
       </c>
       <c r="S14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T14" t="n">
         <v>20</v>
@@ -1815,17 +1815,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>6988348986122602527</t>
+          <t>7582050881475086371</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>喆啡酒店（三河燕郊高铁站永旺梦乐城店）</t>
+          <t>丽枫酒店(廊坊中国医学科学院肿瘤医院店)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>喆啡酒店(三河燕郊高铁站永旺梦乐城店)</t>
+          <t>丽枫酒店(廊坊中国医学科学院肿瘤医院店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1837,15 +1837,15 @@
         <v>92</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,附加分,拿收益</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L15" t="n">
         <v>10</v>
@@ -1857,7 +1857,7 @@
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
@@ -1869,7 +1869,7 @@
         <v>30</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T15" t="n">
         <v>20</v>
@@ -1903,17 +1903,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>7104957003226679299</t>
+          <t>6988348986122602527</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>喆啡酒店（霸州兴华路步行街店）</t>
+          <t>喆啡酒店（三河燕郊高铁站永旺梦乐城店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>喆啡酒店(霸州兴华路步行街店)</t>
+          <t>喆啡酒店(三河燕郊高铁站永旺梦乐城店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6601138217779464200</t>
+          <t>7104957003226679299</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（河北燕郊金燕大街店）</t>
+          <t>喆啡酒店（霸州兴华路步行街店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(河北燕郊金燕大街店)</t>
+          <t>喆啡酒店(霸州兴华路步行街店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2013,11 +2013,11 @@
         <v>92</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2027,13 +2027,13 @@
         <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N17" t="n">
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
@@ -2079,17 +2079,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7462944112841328694</t>
+          <t>6601138217779464200</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0廊坊高铁站店）</t>
+          <t>维也纳国际酒店（河北燕郊金燕大街店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>维也纳酒店(廊坊高铁站店)</t>
+          <t>维也纳国际酒店(河北燕郊金燕大街店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2115,19 +2115,19 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N18" t="n">
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2167,17 +2167,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>6763198105849464840</t>
+          <t>7462944112841328694</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>麗枫酒店·三河燕郊天洋广场店</t>
+          <t>维也纳酒店（5.0廊坊高铁站店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>麗枫酒店(三河燕郊天洋广场店)</t>
+          <t>维也纳酒店(廊坊高铁站店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3043,17 +3043,17 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>7278635549965961257</t>
+          <t>6601251369573681165</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（固安新机场店）</t>
+          <t>维也纳国际酒店（河北廊坊大兴国际机场店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(固安新机场店)</t>
+          <t>维也纳国际酒店(河北廊坊大兴国际机场店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3065,7 +3065,7 @@
         <v>102</v>
       </c>
       <c r="I29" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -3131,26 +3131,26 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>6601251369573681165</t>
+          <t>7346471096587126818</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（河北廊坊大兴国际机场店）</t>
+          <t>维也纳国际酒店（霸州裕华东道亿辰大厦店）</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(河北廊坊大兴国际机场店)</t>
+          <t>维也纳国际酒店(霸州裕华东道亿辰大厦店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
         <v>10</v>
       </c>
       <c r="M30" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N30" t="n">
         <v>30</v>
@@ -3219,29 +3219,29 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>7346471096587126818</t>
+          <t>6601131962893617156</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（霸州裕华东道亿辰大厦店）</t>
+          <t>锦江之星廊坊万达广场店酒店</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(霸州裕华东道亿辰大厦店)</t>
+          <t>锦江之星(廊坊万达广场店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>105</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -3255,19 +3255,19 @@
         <v>10</v>
       </c>
       <c r="M31" t="n">
+        <v>20</v>
+      </c>
+      <c r="N31" t="n">
+        <v>30</v>
+      </c>
+      <c r="O31" t="n">
+        <v>30</v>
+      </c>
+      <c r="P31" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q31" t="n">
         <v>25</v>
-      </c>
-      <c r="N31" t="n">
-        <v>30</v>
-      </c>
-      <c r="O31" t="n">
-        <v>30</v>
-      </c>
-      <c r="P31" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>20</v>
       </c>
       <c r="R31" t="n">
         <v>30</v>
@@ -3307,29 +3307,29 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>6601131962893617156</t>
+          <t>7277461591451240460</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>锦江之星廊坊万达广场店酒店</t>
+          <t>麗枫酒店三河燕郊中央美院店</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>锦江之星(廊坊万达广场店)</t>
+          <t>麗枫酒店(三河燕郊燕顺路中央美院店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>105</v>
       </c>
       <c r="I32" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>10</v>
       </c>
       <c r="M32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N32" t="n">
         <v>30</v>
@@ -3355,7 +3355,7 @@
         <v>30</v>
       </c>
       <c r="Q32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R32" t="n">
         <v>30</v>
@@ -3395,26 +3395,26 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>7277461591451240460</t>
+          <t>7278635549965961257</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>麗枫酒店三河燕郊中央美院店</t>
+          <t>维也纳国际酒店（固安新机场店）</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>麗枫酒店(三河燕郊燕顺路中央美院店)</t>
+          <t>维也纳国际酒店(固安新机场店)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3431,19 +3431,19 @@
         <v>10</v>
       </c>
       <c r="M33" t="n">
+        <v>22</v>
+      </c>
+      <c r="N33" t="n">
+        <v>30</v>
+      </c>
+      <c r="O33" t="n">
+        <v>30</v>
+      </c>
+      <c r="P33" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q33" t="n">
         <v>25</v>
-      </c>
-      <c r="N33" t="n">
-        <v>30</v>
-      </c>
-      <c r="O33" t="n">
-        <v>30</v>
-      </c>
-      <c r="P33" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>20</v>
       </c>
       <c r="R33" t="n">
         <v>30</v>
